--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487406_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487406_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9442</v>
+        <v>8.9247</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2653</v>
+        <v>9.4864</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3211</v>
+        <v>-0.5617</v>
       </c>
       <c r="G2" t="n">
         <v>5.906</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7836</v>
+        <v>0.7641</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0223</v>
+        <v>0.2435</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7612</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.8837</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5036</v>
+        <v>5.8747</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5222</v>
+        <v>5.027</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.8478</v>
       </c>
       <c r="G3" t="n">
         <v>4.3171</v>
@@ -688,13 +688,13 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5194</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8475</v>
+        <v>0.3523</v>
       </c>
       <c r="U3" t="n">
-        <v>0.672</v>
+        <v>0.5383</v>
       </c>
       <c r="V3" t="n">
         <v>0.2754</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>A. GOMEZ LLANES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1813</v>
+        <v>4.1071</v>
       </c>
       <c r="E4" t="n">
-        <v>0.954</v>
+        <v>3.5426</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2273</v>
+        <v>0.5645</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5449</v>
+        <v>2.6921</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0065</v>
+        <v>2.5056</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5513</v>
+        <v>0.1865</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1065</v>
+        <v>2.8089</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.621</v>
+        <v>2.9108</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7275</v>
+        <v>-0.102</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4384</v>
+        <v>-0.1167</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6145</v>
+        <v>-0.4052</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8239</v>
+        <v>0.2885</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7539</v>
+        <v>0.4945</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8267</v>
+        <v>0.4964</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9272</v>
+        <v>-0.0019</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6659</v>
+        <v>0.3329</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6659</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GOMEZ LLANES</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8501</v>
+        <v>3.6953</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5261</v>
+        <v>2.7838</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3239</v>
+        <v>0.9115</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6921</v>
+        <v>2.9429</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5056</v>
+        <v>1.1443</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1865</v>
+        <v>1.7987</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8089</v>
+        <v>2.192</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9108</v>
+        <v>0.9391</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.102</v>
+        <v>1.2529</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1167</v>
+        <v>0.751</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4052</v>
+        <v>0.2052</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2885</v>
+        <v>0.5458</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2374</v>
+        <v>-0.2476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4799</v>
+        <v>-0.0165</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2425</v>
+        <v>-0.2311</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3329</v>
+        <v>0.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4861</v>
+        <v>2.7141</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6815</v>
+        <v>-0.1123</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8046</v>
+        <v>2.8264</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9429</v>
+        <v>1.5449</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1443</v>
+        <v>-0.0065</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7987</v>
+        <v>1.5513</v>
       </c>
       <c r="J6" t="n">
-        <v>2.192</v>
+        <v>0.1065</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9391</v>
+        <v>-0.621</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2529</v>
+        <v>0.7275</v>
       </c>
       <c r="M6" t="n">
-        <v>0.751</v>
+        <v>1.4384</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2052</v>
+        <v>0.6145</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5458</v>
+        <v>0.8239</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.2867</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.3917</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.4569</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.1188</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.3381</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.6083</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.6083</v>
-      </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>M. LATAS CHICO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8867</v>
+        <v>2.2797</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3544</v>
+        <v>3.7619</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5323</v>
+        <v>-1.4823</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3735</v>
+        <v>1.9982</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3191</v>
+        <v>0.26</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6926</v>
+        <v>1.7382</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9141</v>
+        <v>6.5865</v>
       </c>
       <c r="K7" t="n">
-        <v>1.788</v>
+        <v>2.7067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1261</v>
+        <v>3.8798</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5406</v>
+        <v>-4.5883</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1071</v>
+        <v>-2.4467</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5666</v>
+        <v>-2.1416</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1336</v>
+        <v>2.7419</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6711</v>
+        <v>-0.3488</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1235</v>
+        <v>-0.0471</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5476</v>
+        <v>-0.3017</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3329</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>0.1602</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6083</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LATAS CHICO</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7086</v>
+        <v>1.4147</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1908</v>
+        <v>0.1498</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4823</v>
+        <v>1.265</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9982</v>
+        <v>0.3735</v>
       </c>
       <c r="H8" t="n">
-        <v>0.26</v>
+        <v>-0.3191</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7382</v>
+        <v>0.6926</v>
       </c>
       <c r="J8" t="n">
-        <v>6.5865</v>
+        <v>1.9141</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7067</v>
+        <v>1.788</v>
       </c>
       <c r="L8" t="n">
-        <v>3.8798</v>
+        <v>0.1261</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.5883</v>
+        <v>-1.5406</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.4467</v>
+        <v>-2.1071</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1416</v>
+        <v>0.5666</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7419</v>
+        <v>3.1336</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9198</v>
+        <v>0.1991</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6181</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3017</v>
+        <v>0.2803</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8260999999999999</v>
+        <v>-0.3329</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1602</v>
+        <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6659</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1507</v>
+        <v>0.4503</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2947</v>
+        <v>0.6017</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4455</v>
+        <v>-0.1514</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6194</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7479</v>
+        <v>-0.1469</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4576</v>
+        <v>-0.1506</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2904</v>
+        <v>0.0037</v>
       </c>
       <c r="V9" t="n">
         <v>2.4332</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3714</v>
+        <v>-0.1935</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1603</v>
+        <v>-1.9557</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7889</v>
+        <v>1.7622</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4009</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4624</v>
+        <v>-0.2845</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0466</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>1.492</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3041</v>
+        <v>-1.0354</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5391</v>
+        <v>-2.3773</v>
       </c>
       <c r="F11" t="n">
-        <v>1.235</v>
+        <v>1.3419</v>
       </c>
       <c r="G11" t="n">
         <v>-1.393</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3028</v>
+        <v>-0.0341</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.297</v>
+        <v>-0.1353</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0058</v>
+        <v>0.1012</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8457</v>
+        <v>-1.3991</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5305</v>
+        <v>-0.1641</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3152</v>
+        <v>-1.235</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9168</v>
@@ -1390,13 +1390,13 @@
         <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3206</v>
+        <v>0.126</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.297</v>
+        <v>0.0694</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0236</v>
+        <v>0.0566</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3858</v>
+        <v>-1.7359</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3981</v>
+        <v>-0.9887</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9877</v>
+        <v>-0.7472</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2474</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5877</v>
+        <v>0.0622</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4223</v>
+        <v>-0.0129</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1654</v>
+        <v>0.0751</v>
       </c>
       <c r="V13" t="n">
         <v>0.0576</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.5029</v>
+        <v>25.0967</v>
       </c>
       <c r="E14" t="n">
-        <v>19.161</v>
+        <v>19.7551</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3416</v>
+        <v>5.341699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>10.1972</v>
       </c>
       <c r="H14" t="n">
-        <v>6.129700000000001</v>
+        <v>6.1297</v>
       </c>
       <c r="I14" t="n">
         <v>4.067499999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>24.5773</v>
+        <v>24.57730000000001</v>
       </c>
       <c r="K14" t="n">
         <v>17.332</v>
       </c>
       <c r="L14" t="n">
-        <v>7.245199999999998</v>
+        <v>7.2452</v>
       </c>
       <c r="M14" t="n">
         <v>-14.3799</v>
@@ -1546,13 +1546,13 @@
         <v>18.6056</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1673</v>
+        <v>2.7613</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6733000000000006</v>
+        <v>1.2674</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4939</v>
+        <v>1.494</v>
       </c>
       <c r="V14" t="n">
         <v>7.2422</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5229</v>
+        <v>2.1129</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0986</v>
+        <v>2.7126</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5758</v>
+        <v>-0.5997</v>
       </c>
       <c r="G15" t="n">
         <v>1.7583</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0587</v>
+        <v>0.5314</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.297</v>
+        <v>0.317</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2383</v>
+        <v>0.2144</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1767</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CACHOPAS GIL PRATES</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9038</v>
+        <v>-0.5825</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3477</v>
+        <v>-0.4072</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2515</v>
+        <v>-0.1753</v>
       </c>
       <c r="G16" t="n">
-        <v>0.304</v>
+        <v>-0.7936</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6615</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9655</v>
+        <v>-0.0007</v>
       </c>
       <c r="J16" t="n">
-        <v>3.207</v>
+        <v>2.0313</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1258</v>
+        <v>1.5174</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0812</v>
+        <v>0.5139</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.903</v>
+        <v>-2.8249</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7873</v>
+        <v>-2.3102</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1157</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.546</v>
+        <v>0.5875</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3969</v>
+        <v>0.1332</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4493</v>
+        <v>-0.147</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0524</v>
+        <v>0.2803</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9412</v>
+        <v>-0.5097</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6083</v>
+        <v>-0.3329</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3329</v>
+        <v>-0.1767</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>M. CACHOPAS GIL PRATES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1135</v>
+        <v>-1.5059</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6119</v>
+        <v>-0.471</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5017</v>
+        <v>-1.0348</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7936</v>
+        <v>0.304</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-2.6615</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0007</v>
+        <v>2.9655</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0313</v>
+        <v>3.207</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5174</v>
+        <v>0.1258</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5139</v>
+        <v>3.0812</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8249</v>
+        <v>-2.903</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3102</v>
+        <v>-2.7873</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.1157</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5875</v>
+        <v>-2.546</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R17" t="n">
-        <v>2.546</v>
+        <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3978</v>
+        <v>-0.2051</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3517</v>
+        <v>-0.3694</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0461</v>
+        <v>0.1642</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5097</v>
+        <v>0.9412</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>0.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1767</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4593</v>
+        <v>-1.5939</v>
       </c>
       <c r="E18" t="n">
-        <v>0.044</v>
+        <v>-0.4677</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5033</v>
+        <v>-1.1262</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3514</v>
@@ -1858,13 +1858,13 @@
         <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6403</v>
+        <v>0.5056</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8893</v>
+        <v>0.3776</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.249</v>
+        <v>0.1281</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3357</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8016</v>
+        <v>-1.6342</v>
       </c>
       <c r="E19" t="n">
-        <v>0.836</v>
+        <v>-0.2719</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6376</v>
+        <v>-1.3622</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2814</v>
+        <v>-3.8774</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1698</v>
+        <v>0.0592</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1116</v>
+        <v>-3.9366</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4334</v>
+        <v>0.1641</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6655</v>
+        <v>2.9142</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7679</v>
+        <v>-2.7501</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.152</v>
+        <v>-4.0415</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4957</v>
+        <v>-2.855</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6563</v>
+        <v>-1.1865</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3709</v>
+        <v>1.3709</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5875</v>
+        <v>2.546</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5046</v>
+        <v>-0.11</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3611</v>
+        <v>-0.4199</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1435</v>
+        <v>0.31</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2166</v>
+        <v>0.9823</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>-0.1767</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9353</v>
+        <v>-1.6384</v>
       </c>
       <c r="E20" t="n">
         <v>-1.4409</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4944</v>
+        <v>-0.1975</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0977</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7776</v>
+        <v>-0.4808</v>
       </c>
       <c r="T20" t="n">
         <v>-0.5346</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.243</v>
+        <v>0.0538</v>
       </c>
       <c r="V20" t="n">
         <v>0.1152</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9478</v>
+        <v>-1.8694</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9694</v>
+        <v>2.0718</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9172</v>
+        <v>-3.9411</v>
       </c>
       <c r="G21" t="n">
         <v>1.1351</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2787</v>
+        <v>-0.2003</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0538</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8249</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1413</v>
+        <v>-1.9546</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4766</v>
+        <v>0.7337</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6646</v>
+        <v>-2.6883</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8774</v>
+        <v>0.2814</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0592</v>
+        <v>0.1698</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.9366</v>
+        <v>0.1116</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1641</v>
+        <v>2.4334</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9142</v>
+        <v>1.6655</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.7501</v>
+        <v>0.7679</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.0415</v>
+        <v>-2.152</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.855</v>
+        <v>-1.4957</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1865</v>
+        <v>-0.6563</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3709</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1751</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>2.546</v>
+        <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6171</v>
+        <v>0.3516</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6246</v>
+        <v>0.2588</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0075</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9823</v>
+        <v>-1.2166</v>
       </c>
       <c r="W22" t="n">
-        <v>1.159</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1767</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2968</v>
+        <v>-3.1023</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6262</v>
+        <v>-2.7285</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6706</v>
+        <v>-0.3738</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5943</v>
@@ -2248,13 +2248,13 @@
         <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1548</v>
+        <v>0.0397</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0882</v>
+        <v>-0.0141</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.243</v>
+        <v>0.0538</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1767</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4613</v>
+        <v>-5.0685</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8582</v>
+        <v>-3.5512</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6031</v>
+        <v>-1.5173</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9519</v>
@@ -2326,13 +2326,13 @@
         <v>0.7834</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7652</v>
+        <v>-0.3724</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7963</v>
+        <v>-0.4893</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0311</v>
+        <v>0.1169</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3318</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.965</v>
+        <v>-5.6193</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6237</v>
+        <v>-1.5213</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.3413</v>
+        <v>-4.0979</v>
       </c>
       <c r="G25" t="n">
         <v>-2.0097</v>
@@ -2404,13 +2404,13 @@
         <v>0.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6592</v>
+        <v>-0.3135</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3211</v>
+        <v>-0.2188</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3381</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-2.7086</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-24.5028</v>
+        <v>-22.4561</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3418</v>
+        <v>-5.3416</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.1611</v>
+        <v>-17.1141</v>
       </c>
       <c r="G26" t="n">
         <v>-10.1972</v>
@@ -2452,7 +2452,7 @@
         <v>-6.1295</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.067600000000001</v>
+        <v>-4.067599999999999</v>
       </c>
       <c r="J26" t="n">
         <v>14.3799</v>
@@ -2473,7 +2473,7 @@
         <v>-7.2452</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.896199999999999</v>
+        <v>-4.8962</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.6056</v>
@@ -2482,13 +2482,13 @@
         <v>13.7092</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.1673</v>
+        <v>-0.1206</v>
       </c>
       <c r="T26" t="n">
         <v>-1.4938</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6734</v>
+        <v>1.3734</v>
       </c>
       <c r="V26" t="n">
         <v>-7.242000000000001</v>
@@ -2497,7 +2497,7 @@
         <v>0.3779999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.619900000000001</v>
+        <v>-7.619899999999999</v>
       </c>
     </row>
   </sheetData>
